--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.925743849</v>
+        <v>46157.93117653383</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117653383</v>
+        <v>46157.93183453434</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183453434</v>
+        <v>46157.93405671686</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405671686</v>
+        <v>46157.93723756199</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723756199</v>
+        <v>46158.28221528161</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221528161</v>
+        <v>46158.29701993061</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29701993061</v>
+        <v>46158.29821269136</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821269136</v>
+        <v>46158.33392569992</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392569992</v>
+        <v>46158.36862334921</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Шакалов-слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862334921</v>
+        <v>46158.37293314619</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
